--- a/Resultados Finais/Resultado Final - Classificação dos Itens de Prova.xlsx
+++ b/Resultados Finais/Resultado Final - Classificação dos Itens de Prova.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{118FECC6-9110-4EF4-8094-660D44575BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8C62184-5F99-44A9-BFF8-41BCCCBF6DAC}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{118FECC6-9110-4EF4-8094-660D44575BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB33843E-4C87-489C-B0A4-F45DEFB0BC56}"/>
   <bookViews>
-    <workbookView xWindow="29388" yWindow="-81" windowWidth="29698" windowHeight="16094" tabRatio="875" firstSheet="2" activeTab="2" xr2:uid="{A3D81B84-84E8-4574-A2BD-4114E0857E83}"/>
+    <workbookView xWindow="30252" yWindow="783" windowWidth="22118" windowHeight="11613" tabRatio="875" firstSheet="2" activeTab="2" xr2:uid="{A3D81B84-84E8-4574-A2BD-4114E0857E83}"/>
   </bookViews>
   <sheets>
     <sheet name="Quadro Geral" sheetId="27" r:id="rId1"/>
@@ -3433,10 +3428,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -3727,7 +3718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06EE189-C818-4EB3-8C85-4817F7812831}">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.59765625" style="5" customWidth="1"/>
@@ -4708,13 +4699,14 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B426E9F1-E20A-4BB4-BE38-4BA1B62693D4}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.796875" customWidth="1"/>
@@ -5015,12 +5007,12 @@
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
     </row>
-    <row r="33" customFormat="1" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A31:C31"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5332,6 +5324,7 @@
     <mergeCell ref="A30:C30"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5536,6 +5529,7 @@
     <cfRule type="uniqueValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5742,6 +5736,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5943,6 +5938,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6149,6 +6145,7 @@
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6350,6 +6347,7 @@
     <mergeCell ref="A21:C21"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6548,6 +6546,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6771,6 +6770,7 @@
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6988,12 +6988,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BD3BE1-C84F-4C86-AEE8-F3BC28FB6114}">
-  <dimension ref="B1:H30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.796875" customWidth="1"/>
@@ -7336,7 +7337,8 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7538,6 +7540,7 @@
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7744,6 +7747,7 @@
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7940,6 +7944,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8141,6 +8146,7 @@
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8359,6 +8365,7 @@
     <mergeCell ref="B23:D23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8577,6 +8584,7 @@
     <mergeCell ref="B23:D23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8777,6 +8785,7 @@
     <mergeCell ref="B23:C23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8976,6 +8985,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9176,6 +9186,7 @@
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9185,6 +9196,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9462,6 +9474,7 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9745,6 +9758,7 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10028,6 +10042,7 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10311,6 +10326,7 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10624,12 +10640,13 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE73208A-B102-4257-9A4F-53796B152CED}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.59765625" style="5" customWidth="1"/>
@@ -10881,6 +10898,7 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11194,5 +11212,6 @@
     <mergeCell ref="A32:C32"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>